--- a/outputs/Block5_Largest_Adjustments.xlsx
+++ b/outputs/Block5_Largest_Adjustments.xlsx
@@ -106,73 +106,73 @@
     <t>Model Stability</t>
   </si>
   <si>
+    <t>RSenSafResH (&gt;10%)</t>
+  </si>
+  <si>
     <t>RHouSafResH (&gt;10%)</t>
   </si>
   <si>
     <t>DHouSafResH (&gt;5%&lt;=10%)</t>
   </si>
   <si>
-    <t>RSenSafResH (&gt;10%)</t>
-  </si>
-  <si>
     <t>DSenSafResH (&gt;10%)</t>
   </si>
   <si>
-    <t>RHouLeanResH  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>RHouLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RSenLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RHouLikResLD (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RHouSafResLD (&gt;10%)</t>
+    <t>RHouTiltResLD (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RHouTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DHouLikResLR (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DSenLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DHouLeanResLR  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>RSenSafResLD (&gt;10%)</t>
   </si>
   <si>
     <t>RSenTiltResLD (&lt;=1%)</t>
   </si>
   <si>
-    <t>DHouLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>DHouTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RSenSafResLD (&gt;10%)</t>
-  </si>
-  <si>
-    <t>DSenLikResLR (&gt;5%&lt;=10%)</t>
+    <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>RSenTiltResH (&lt;=1%)</t>
   </si>
   <si>
     <t>DHouTiltResLR (&lt;=1%)</t>
   </si>
   <si>
+    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>Senate Buckets</t>
+  </si>
+  <si>
     <t>House Buckets</t>
   </si>
   <si>
-    <t>Senate Buckets</t>
-  </si>
-  <si>
     <t>ML Predicted</t>
   </si>
   <si>
     <t>Integer</t>
   </si>
   <si>
+    <t>High sensitivity</t>
+  </si>
+  <si>
+    <t>Low sensitivity</t>
+  </si>
+  <si>
+    <t>Moderate-low sensitivity</t>
+  </si>
+  <si>
     <t>Moderate sensitivity</t>
-  </si>
-  <si>
-    <t>High sensitivity</t>
-  </si>
-  <si>
-    <t>Very high sensitivity</t>
-  </si>
-  <si>
-    <t>Moderate-low sensitivity</t>
   </si>
 </sst>
 </file>
@@ -633,79 +633,79 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>173.296</v>
+        <v>10.028</v>
       </c>
       <c r="D2">
-        <v>175.72</v>
+        <v>11.468</v>
       </c>
       <c r="E2">
-        <v>182.3239848953666</v>
+        <v>13.28203815275881</v>
       </c>
       <c r="F2">
-        <v>172.6</v>
+        <v>11.6</v>
       </c>
       <c r="G2">
-        <v>174.4659250965879</v>
+        <v>10.70483610671818</v>
       </c>
       <c r="J2" t="s">
         <v>4</v>
       </c>
       <c r="K2">
-        <v>182.3239848953666</v>
+        <v>13.28203815275881</v>
       </c>
       <c r="L2">
-        <v>24.70132137894479</v>
+        <v>3.050242274051084</v>
       </c>
       <c r="M2">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N2">
-        <v>18.7</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="s">
         <v>47</v>
       </c>
       <c r="P2">
-        <v>170.7162008332492</v>
+        <v>15.15860750983988</v>
       </c>
       <c r="Q2">
-        <v>0.9363343003457338</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R2">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="S2" t="s">
         <v>48</v>
       </c>
       <c r="T2">
-        <v>-11.60778406211739</v>
+        <v>1.876569357081072</v>
       </c>
       <c r="U2">
-        <v>0.2837991667507822</v>
+        <v>-0.158607509839884</v>
       </c>
       <c r="V2" t="s">
         <v>6</v>
       </c>
       <c r="W2">
-        <v>174.4659250965879</v>
+        <v>10.70483610671818</v>
       </c>
       <c r="X2">
-        <v>7.858059798778754</v>
+        <v>2.577202046040632</v>
       </c>
       <c r="Y2">
-        <v>11.32398489536661</v>
+        <v>1.717961847241188</v>
       </c>
       <c r="Z2">
-        <v>0.3181230541568072</v>
+        <v>0.8449171621432557</v>
       </c>
       <c r="AA2">
-        <v>0.4584364019092145</v>
+        <v>0.5632214404266095</v>
       </c>
       <c r="AB2">
-        <v>1.320926276948919</v>
+        <v>0.544686120366265</v>
       </c>
       <c r="AC2">
-        <v>69.26484290771914</v>
+        <v>47.41063290551929</v>
       </c>
       <c r="AD2" t="s">
         <v>49</v>
@@ -716,82 +716,82 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3">
-        <v>173.312</v>
+        <v>172.1</v>
       </c>
       <c r="D3">
-        <v>170.552</v>
+        <v>175.156</v>
       </c>
       <c r="E3">
-        <v>176.0063243272117</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="F3">
-        <v>169.2</v>
+        <v>172.6</v>
       </c>
       <c r="G3">
-        <v>171.9799070682415</v>
+        <v>173.5749550722659</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>176.0063243272117</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="L3">
-        <v>4.764861070548267</v>
+        <v>24.70132137894479</v>
       </c>
       <c r="M3">
         <v>5.24749619700716</v>
       </c>
       <c r="N3">
-        <v>13.2</v>
+        <v>18.7</v>
       </c>
       <c r="O3" t="s">
         <v>47</v>
       </c>
       <c r="P3">
-        <v>181.3185762509099</v>
+        <v>173.8081494148196</v>
       </c>
       <c r="Q3">
-        <v>1.030182165010288</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R3">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="S3" t="s">
         <v>48</v>
       </c>
       <c r="T3">
-        <v>5.31225192369817</v>
+        <v>-1.781713658384717</v>
       </c>
       <c r="U3">
-        <v>-0.3185762509098993</v>
+        <v>0.1918505851803616</v>
       </c>
       <c r="V3" t="s">
         <v>6</v>
       </c>
       <c r="W3">
-        <v>171.9799070682415</v>
+        <v>173.5749550722659</v>
       </c>
       <c r="X3">
-        <v>4.026417258970184</v>
+        <v>2.014908000938448</v>
       </c>
       <c r="Y3">
-        <v>4.993675672788271</v>
+        <v>1.589863073204356</v>
       </c>
       <c r="Z3">
-        <v>0.845023013127828</v>
+        <v>0.08157085890376452</v>
       </c>
       <c r="AA3">
-        <v>1.04802125368446</v>
+        <v>0.06436348277948976</v>
       </c>
       <c r="AB3">
-        <v>0.3609743235263839</v>
+        <v>1.320926276948919</v>
       </c>
       <c r="AC3">
-        <v>40.00873433552916</v>
+        <v>92.72349650896915</v>
       </c>
       <c r="AD3" t="s">
         <v>50</v>
@@ -805,82 +805,82 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>10.056</v>
+        <v>172.984</v>
       </c>
       <c r="D4">
-        <v>11.612</v>
+        <v>170.488</v>
       </c>
       <c r="E4">
-        <v>12.72721886527684</v>
+        <v>172.6467820636017</v>
       </c>
       <c r="F4">
-        <v>11.6</v>
+        <v>169.2</v>
       </c>
       <c r="G4">
-        <v>10.78735901531492</v>
+        <v>171.7793246530184</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>12.72721886527684</v>
+        <v>172.6467820636017</v>
       </c>
       <c r="L4">
-        <v>3.050242274051084</v>
+        <v>4.764861070548267</v>
       </c>
       <c r="M4">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N4">
-        <v>5.6</v>
+        <v>13.2</v>
       </c>
       <c r="O4" t="s">
         <v>47</v>
       </c>
       <c r="P4">
-        <v>14.76027887619046</v>
+        <v>174.4769462223457</v>
       </c>
       <c r="Q4">
-        <v>1.159741105455516</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R4">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="S4" t="s">
         <v>48</v>
       </c>
       <c r="T4">
-        <v>2.033060010913617</v>
+        <v>1.830164158743969</v>
       </c>
       <c r="U4">
-        <v>0.2397211238095416</v>
+        <v>-0.4769462223457026</v>
       </c>
       <c r="V4" t="s">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>10.78735901531492</v>
+        <v>171.7793246530184</v>
       </c>
       <c r="X4">
-        <v>1.939859849961922</v>
+        <v>0.8674574105832846</v>
       </c>
       <c r="Y4">
-        <v>2.272781134723159</v>
+        <v>1.353217936398266</v>
       </c>
       <c r="Z4">
-        <v>0.6359691052952189</v>
+        <v>0.1820530331818197</v>
       </c>
       <c r="AA4">
-        <v>0.7451149549850793</v>
+        <v>0.2839994527358924</v>
       </c>
       <c r="AB4">
-        <v>0.544686120366265</v>
+        <v>0.3609743235263839</v>
       </c>
       <c r="AC4">
-        <v>50.95791180581695</v>
+        <v>80.43391422492162</v>
       </c>
       <c r="AD4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -888,28 +888,28 @@
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5">
-        <v>13.152</v>
+        <v>13.232</v>
       </c>
       <c r="D5">
-        <v>12.22</v>
+        <v>12.328</v>
       </c>
       <c r="E5">
-        <v>11.17487741647244</v>
+        <v>11.23658004704028</v>
       </c>
       <c r="F5">
         <v>12.4</v>
       </c>
       <c r="G5">
-        <v>12.71393663092962</v>
+        <v>12.8070973330047</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>11.17487741647244</v>
+        <v>11.23658004704028</v>
       </c>
       <c r="L5">
         <v>2.351026032651849</v>
@@ -924,49 +924,49 @@
         <v>47</v>
       </c>
       <c r="P5">
-        <v>9.132471991736034</v>
+        <v>9.674452691001546</v>
       </c>
       <c r="Q5">
-        <v>0.8172324090351291</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S5" t="s">
         <v>48</v>
       </c>
       <c r="T5">
-        <v>-2.04240542473641</v>
+        <v>-1.562127356038731</v>
       </c>
       <c r="U5">
-        <v>-0.1324719917360344</v>
+        <v>0.3255473089984537</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>12.71393663092962</v>
+        <v>12.8070973330047</v>
       </c>
       <c r="X5">
-        <v>1.539059214457176</v>
+        <v>1.570517285964419</v>
       </c>
       <c r="Y5">
-        <v>2.174877416472444</v>
+        <v>1.236580047040277</v>
       </c>
       <c r="Z5">
-        <v>0.6546329955866917</v>
+        <v>0.6680135669076143</v>
       </c>
       <c r="AA5">
-        <v>0.9250758546553748</v>
+        <v>0.5259746297430284</v>
       </c>
       <c r="AB5">
         <v>0.6530627868477359</v>
       </c>
       <c r="AC5">
-        <v>47.27029992542463</v>
+        <v>53.88597538332969</v>
       </c>
       <c r="AD5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -974,85 +974,85 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6">
-        <v>13.488</v>
+        <v>1.832</v>
       </c>
       <c r="D6">
-        <v>12.544</v>
+        <v>1.772</v>
       </c>
       <c r="E6">
-        <v>15.02106749310035</v>
+        <v>2.554644495322226</v>
       </c>
       <c r="F6">
-        <v>11.8</v>
+        <v>1.6</v>
       </c>
       <c r="G6">
-        <v>13.03238560594928</v>
+        <v>1.803041458005251</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>15.02106749310035</v>
+        <v>2.554644495322226</v>
       </c>
       <c r="L6">
-        <v>3.125306797245826</v>
+        <v>1.198624596172324</v>
       </c>
       <c r="M6">
         <v>5.24749619700716</v>
       </c>
       <c r="N6">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="s">
         <v>47</v>
       </c>
       <c r="P6">
-        <v>14.06474072159816</v>
+        <v>2.528722469358031</v>
       </c>
       <c r="Q6">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="S6" t="s">
         <v>48</v>
       </c>
       <c r="T6">
-        <v>-0.956326771502189</v>
+        <v>-0.02592202596419435</v>
       </c>
       <c r="U6">
-        <v>-0.06474072159816124</v>
+        <v>-0.5287224693580312</v>
       </c>
       <c r="V6" t="s">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>13.03238560594928</v>
+        <v>1.803041458005251</v>
       </c>
       <c r="X6">
-        <v>1.988681887151071</v>
+        <v>0.7516030373169746</v>
       </c>
       <c r="Y6">
-        <v>1.02106749310035</v>
+        <v>0.5546444953222256</v>
       </c>
       <c r="Z6">
-        <v>0.6363157335156967</v>
+        <v>0.627054575483547</v>
       </c>
       <c r="AA6">
-        <v>0.3267095230459183</v>
+        <v>0.4627341179994319</v>
       </c>
       <c r="AB6">
-        <v>0.6511055827595471</v>
+        <v>0.7491403726077025</v>
       </c>
       <c r="AC6">
-        <v>58.9810747875693</v>
+        <v>56.57842736664286</v>
       </c>
       <c r="AD6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1060,85 +1060,85 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7">
-        <v>15.112</v>
+        <v>3.692</v>
       </c>
       <c r="D7">
-        <v>15.028</v>
+        <v>3.192</v>
       </c>
       <c r="E7">
-        <v>17.90152433308469</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="F7">
-        <v>14.2</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>15.07145804120735</v>
+        <v>3.450678816710424</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>17.90152433308469</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="L7">
-        <v>6.129350049043507</v>
+        <v>0.887818750560327</v>
       </c>
       <c r="M7">
         <v>5.24749619700716</v>
       </c>
       <c r="N7">
-        <v>6.3</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="s">
         <v>47</v>
       </c>
       <c r="P7">
-        <v>16.76181126154098</v>
+        <v>3.440193613933819</v>
       </c>
       <c r="Q7">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R7">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S7" t="s">
         <v>48</v>
       </c>
       <c r="T7">
-        <v>-1.13971307154371</v>
+        <v>-0.03526554980344976</v>
       </c>
       <c r="U7">
-        <v>0.2381887384590158</v>
+        <v>-0.4401936139338187</v>
       </c>
       <c r="V7" t="s">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>15.07145804120735</v>
+        <v>3.450678816710424</v>
       </c>
       <c r="X7">
-        <v>2.830066291877342</v>
+        <v>0.0247803470268444</v>
       </c>
       <c r="Y7">
-        <v>0.9015243330846943</v>
+        <v>0.4754591637372685</v>
       </c>
       <c r="Z7">
-        <v>0.4617237177241946</v>
+        <v>0.02791149320872625</v>
       </c>
       <c r="AA7">
-        <v>0.1470831859611899</v>
+        <v>0.5355362943587225</v>
       </c>
       <c r="AB7">
-        <v>0.972912706197382</v>
+        <v>0.3551275002241308</v>
       </c>
       <c r="AC7">
-        <v>70.35618198382974</v>
+        <v>81.41748166151876</v>
       </c>
       <c r="AD7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1149,79 +1149,79 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>1.148</v>
+        <v>3.184</v>
       </c>
       <c r="D8">
-        <v>1.224</v>
+        <v>4.004</v>
       </c>
       <c r="E8">
-        <v>2.2065080011038</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="G8">
-        <v>1.183721905632348</v>
+        <v>3.579766740594905</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>2.2065080011038</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="L8">
-        <v>0.8500971208676269</v>
+        <v>7.059923274159115</v>
       </c>
       <c r="M8">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N8">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="O8" t="s">
         <v>47</v>
       </c>
       <c r="P8">
-        <v>2.558978028396561</v>
+        <v>1.566812662552681</v>
       </c>
       <c r="Q8">
-        <v>1.159741105455516</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8" t="s">
         <v>48</v>
       </c>
       <c r="T8">
-        <v>0.3524700272927612</v>
+        <v>0.01643497574066832</v>
       </c>
       <c r="U8">
-        <v>0.4410219716034391</v>
+        <v>0.433187337447319</v>
       </c>
       <c r="V8" t="s">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>1.183721905632348</v>
+        <v>3.579766740594905</v>
       </c>
       <c r="X8">
-        <v>1.022786095471451</v>
+        <v>2.029389053782892</v>
       </c>
       <c r="Y8">
-        <v>0.7934919988962004</v>
+        <v>0.4496223131879873</v>
       </c>
       <c r="Z8">
-        <v>1.203140288756154</v>
+        <v>0.2874519984106493</v>
       </c>
       <c r="AA8">
-        <v>0.933413347037743</v>
+        <v>0.06368657218042365</v>
       </c>
       <c r="AB8">
-        <v>1.700194241735254</v>
+        <v>0.9289372729156731</v>
       </c>
       <c r="AC8">
-        <v>32.99758334560023</v>
+        <v>81.12864354622022</v>
       </c>
       <c r="AD8" t="s">
         <v>51</v>
@@ -1235,82 +1235,82 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>7.252</v>
+        <v>1.9</v>
       </c>
       <c r="D9">
-        <v>5.608</v>
+        <v>1.54</v>
       </c>
       <c r="E9">
-        <v>4.766317009415515</v>
+        <v>1.430889012604439</v>
       </c>
       <c r="F9">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="G9">
-        <v>6.458535949343873</v>
+        <v>1.730790973320455</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>4.766317009415515</v>
+        <v>1.430889012604439</v>
       </c>
       <c r="L9">
-        <v>3.997862832988686</v>
+        <v>1.157976831184469</v>
       </c>
       <c r="M9">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N9">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="s">
         <v>47</v>
       </c>
       <c r="P9">
-        <v>4.462866102237046</v>
+        <v>1.231964530182992</v>
       </c>
       <c r="Q9">
-        <v>0.9363343003457338</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S9" t="s">
         <v>48</v>
       </c>
       <c r="T9">
-        <v>-0.3034509071784681</v>
+        <v>-0.1989244824214469</v>
       </c>
       <c r="U9">
-        <v>-0.4628661022370464</v>
+        <v>-0.2319645301829925</v>
       </c>
       <c r="V9" t="s">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>6.458535949343873</v>
+        <v>1.730790973320455</v>
       </c>
       <c r="X9">
-        <v>1.692218939928359</v>
+        <v>0.2999019607160154</v>
       </c>
       <c r="Y9">
-        <v>0.7663170094155145</v>
+        <v>0.4308890126044393</v>
       </c>
       <c r="Z9">
-        <v>0.4232808904709982</v>
+        <v>0.2589878766479743</v>
       </c>
       <c r="AA9">
-        <v>0.1916816662873444</v>
+        <v>0.3721050378561482</v>
       </c>
       <c r="AB9">
-        <v>0.5966959452221919</v>
+        <v>0.8271263079889064</v>
       </c>
       <c r="AC9">
-        <v>71.01911200459742</v>
+        <v>74.18717584194117</v>
       </c>
       <c r="AD9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -1318,85 +1318,85 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10">
-        <v>5.232</v>
+        <v>3.54</v>
       </c>
       <c r="D10">
-        <v>4.208</v>
+        <v>4.812</v>
       </c>
       <c r="E10">
-        <v>3.696547591818899</v>
+        <v>5.586198698614951</v>
       </c>
       <c r="F10">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>4.737774216622949</v>
+        <v>4.153921090288683</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>3.696547591818899</v>
+        <v>5.586198698614951</v>
       </c>
       <c r="L10">
-        <v>2.858585552684069</v>
+        <v>2.262338789582505</v>
       </c>
       <c r="M10">
         <v>5.24749619700716</v>
       </c>
       <c r="N10">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="O10" t="s">
         <v>47</v>
       </c>
       <c r="P10">
-        <v>3.461204303080457</v>
+        <v>5.645415907992541</v>
       </c>
       <c r="Q10">
-        <v>0.9363343003457338</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S10" t="s">
         <v>48</v>
       </c>
       <c r="T10">
-        <v>-0.2353432887384428</v>
+        <v>0.05921720937758934</v>
       </c>
       <c r="U10">
-        <v>-0.4612043030804567</v>
+        <v>0.3545840920074594</v>
       </c>
       <c r="V10" t="s">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>4.737774216622949</v>
+        <v>4.153921090288683</v>
       </c>
       <c r="X10">
-        <v>1.041226624804049</v>
+        <v>1.432277608326268</v>
       </c>
       <c r="Y10">
-        <v>0.6965475918188995</v>
+        <v>0.4138013013850488</v>
       </c>
       <c r="Z10">
-        <v>0.3642453953586904</v>
+        <v>0.633095986737947</v>
       </c>
       <c r="AA10">
-        <v>0.2436686182664276</v>
+        <v>0.1829086356519627</v>
       </c>
       <c r="AB10">
-        <v>0.6972159884595291</v>
+        <v>0.452467757916501</v>
       </c>
       <c r="AC10">
-        <v>72.46666497041721</v>
+        <v>62.15552874778314</v>
       </c>
       <c r="AD10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -1404,28 +1404,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11">
-        <v>0.656</v>
+        <v>0.632</v>
       </c>
       <c r="D11">
-        <v>0.384</v>
+        <v>0.416</v>
       </c>
       <c r="E11">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="F11">
         <v>0.4</v>
       </c>
       <c r="G11">
-        <v>0.5281531798421215</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="L11">
         <v>0.7620693762924241</v>
@@ -1440,10 +1440,10 @@
         <v>47</v>
       </c>
       <c r="P11">
-        <v>0.5063526117264946</v>
+        <v>0.7484613503089816</v>
       </c>
       <c r="Q11">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -1452,37 +1452,37 @@
         <v>48</v>
       </c>
       <c r="T11">
-        <v>0.06974429514224045</v>
+        <v>0.0926562439219849</v>
       </c>
       <c r="U11">
-        <v>0.4936473882735054</v>
+        <v>0.2515386496910184</v>
       </c>
       <c r="V11" t="s">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>0.5281531798421215</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="X11">
-        <v>0.09154486325786737</v>
+        <v>0.1253305223947238</v>
       </c>
       <c r="Y11">
-        <v>0.5633916834157459</v>
+        <v>0.3441948936130033</v>
       </c>
       <c r="Z11">
-        <v>0.1201266788901112</v>
+        <v>0.1644607778421363</v>
       </c>
       <c r="AA11">
-        <v>0.7392918557582336</v>
+        <v>0.4516582142265844</v>
       </c>
       <c r="AB11">
         <v>0.95258672036553</v>
       </c>
       <c r="AC11">
-        <v>71.40270081666996</v>
+        <v>76.72213858724069</v>
       </c>
       <c r="AD11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:30">
@@ -1493,82 +1493,82 @@
         <v>45</v>
       </c>
       <c r="C12">
-        <v>13.792</v>
+        <v>0.632</v>
       </c>
       <c r="D12">
-        <v>14.964</v>
+        <v>0.416</v>
       </c>
       <c r="E12">
-        <v>18.4418098343119</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="F12">
-        <v>14.6</v>
+        <v>0.4</v>
       </c>
       <c r="G12">
-        <v>14.35765685363077</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="J12" t="s">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>18.4418098343119</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="L12">
-        <v>5.333756871724871</v>
+        <v>0.7620693762924241</v>
       </c>
       <c r="M12">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N12">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="O12" t="s">
         <v>47</v>
       </c>
       <c r="P12">
-        <v>18.99842358181946</v>
+        <v>0.7484613503089816</v>
       </c>
       <c r="Q12">
-        <v>1.030182165010288</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R12">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="S12" t="s">
         <v>48</v>
       </c>
       <c r="T12">
-        <v>0.556613747507555</v>
+        <v>0.0926562439219849</v>
       </c>
       <c r="U12">
-        <v>0.001576418180540884</v>
+        <v>0.2515386496910184</v>
       </c>
       <c r="V12" t="s">
         <v>6</v>
       </c>
       <c r="W12">
-        <v>14.35765685363077</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="X12">
-        <v>4.084152980681136</v>
+        <v>0.1253305223947238</v>
       </c>
       <c r="Y12">
-        <v>0.5581901656880959</v>
+        <v>0.3441948936130033</v>
       </c>
       <c r="Z12">
-        <v>0.7657178755807014</v>
+        <v>0.1644607778421363</v>
       </c>
       <c r="AA12">
-        <v>0.1046523452628961</v>
+        <v>0.4516582142265844</v>
       </c>
       <c r="AB12">
-        <v>1.088521810556096</v>
+        <v>0.95258672036553</v>
       </c>
       <c r="AC12">
-        <v>58.6053064371732</v>
+        <v>76.72213858724069</v>
       </c>
       <c r="AD12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:30">
@@ -1579,82 +1579,82 @@
         <v>45</v>
       </c>
       <c r="C13">
-        <v>1.092</v>
+        <v>0.612</v>
       </c>
       <c r="D13">
-        <v>1.224</v>
+        <v>0.732</v>
       </c>
       <c r="E13">
-        <v>0.5513716620292705</v>
+        <v>0.3293773794100608</v>
       </c>
       <c r="F13">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="G13">
-        <v>1.155708792388448</v>
+        <v>0.6684030088931816</v>
       </c>
       <c r="J13" t="s">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>0.5513716620292705</v>
+        <v>0.3293773794100608</v>
       </c>
       <c r="L13">
-        <v>0.8200692764238203</v>
+        <v>1.559831022862906</v>
       </c>
       <c r="M13">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N13">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O13" t="s">
         <v>47</v>
       </c>
       <c r="P13">
-        <v>0.5680132525146347</v>
+        <v>0.2835868085528425</v>
       </c>
       <c r="Q13">
-        <v>1.030182165010288</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="s">
         <v>48</v>
       </c>
       <c r="T13">
-        <v>0.01664159048536429</v>
+        <v>-0.04579057085721838</v>
       </c>
       <c r="U13">
-        <v>0.4319867474853653</v>
+        <v>-0.2835868085528425</v>
       </c>
       <c r="V13" t="s">
         <v>6</v>
       </c>
       <c r="W13">
-        <v>1.155708792388448</v>
+        <v>0.6684030088931816</v>
       </c>
       <c r="X13">
-        <v>0.6043371303591779</v>
+        <v>0.3390256294831208</v>
       </c>
       <c r="Y13">
-        <v>0.4486283379707295</v>
+        <v>0.3293773794100608</v>
       </c>
       <c r="Z13">
-        <v>0.7369342416955152</v>
+        <v>0.2173476642751179</v>
       </c>
       <c r="AA13">
-        <v>0.5470615115921911</v>
+        <v>0.2111622185879616</v>
       </c>
       <c r="AB13">
-        <v>0.7455175240216548</v>
+        <v>1.299859185719089</v>
       </c>
       <c r="AC13">
-        <v>51.14636374435788</v>
+        <v>80.63940515159102</v>
       </c>
       <c r="AD13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:30">
@@ -1662,85 +1662,85 @@
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14">
-        <v>0.656</v>
+        <v>0.164</v>
       </c>
       <c r="D14">
-        <v>0.384</v>
+        <v>0.268</v>
       </c>
       <c r="E14">
-        <v>0.4366083165842541</v>
+        <v>0.6905082799680116</v>
       </c>
       <c r="F14">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G14">
-        <v>0.5281531798421215</v>
+        <v>0.2128826077074241</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
       </c>
       <c r="K14">
-        <v>0.4366083165842541</v>
+        <v>0.6905082799680116</v>
       </c>
       <c r="L14">
-        <v>0.7620693762924241</v>
+        <v>0.4925498319332764</v>
       </c>
       <c r="M14">
         <v>1.038416113387647</v>
       </c>
       <c r="N14">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="O14" t="s">
         <v>47</v>
       </c>
       <c r="P14">
-        <v>0.5063526117264946</v>
+        <v>0.7880676051329962</v>
       </c>
       <c r="Q14">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="s">
         <v>48</v>
       </c>
       <c r="T14">
-        <v>0.06974429514224045</v>
+        <v>0.09755932516498467</v>
       </c>
       <c r="U14">
-        <v>-0.5063526117264946</v>
+        <v>0.2119323948670038</v>
       </c>
       <c r="V14" t="s">
         <v>6</v>
       </c>
       <c r="W14">
-        <v>0.5281531798421215</v>
+        <v>0.2128826077074241</v>
       </c>
       <c r="X14">
-        <v>0.09154486325786737</v>
+        <v>0.4776256722605874</v>
       </c>
       <c r="Y14">
-        <v>0.4366083165842541</v>
+        <v>0.3094917200319884</v>
       </c>
       <c r="Z14">
-        <v>0.1201266788901112</v>
+        <v>0.9697002035020272</v>
       </c>
       <c r="AA14">
-        <v>0.5729246314927595</v>
+        <v>0.6283460067730039</v>
       </c>
       <c r="AB14">
-        <v>0.95258672036553</v>
+        <v>1.231374579833191</v>
       </c>
       <c r="AC14">
-        <v>75.68380671977501</v>
+        <v>42.73182468197061</v>
       </c>
       <c r="AD14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:30">
@@ -1751,82 +1751,82 @@
         <v>46</v>
       </c>
       <c r="C15">
-        <v>0.652</v>
+        <v>1.412</v>
       </c>
       <c r="D15">
-        <v>0.612</v>
+        <v>1.808</v>
       </c>
       <c r="E15">
-        <v>0.2977289224579263</v>
+        <v>1.699906626866217</v>
       </c>
       <c r="F15">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="G15">
-        <v>0.633198997035606</v>
+        <v>1.603126377165344</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
       </c>
       <c r="K15">
-        <v>0.2977289224579263</v>
+        <v>1.699906626866217</v>
       </c>
       <c r="L15">
-        <v>1.005444112310955</v>
+        <v>1.746417103282563</v>
       </c>
       <c r="M15">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N15">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="s">
         <v>47</v>
       </c>
       <c r="P15">
-        <v>0.2433137245397242</v>
+        <v>1.717926703142854</v>
       </c>
       <c r="Q15">
-        <v>0.8172324090351291</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S15" t="s">
         <v>48</v>
       </c>
       <c r="T15">
-        <v>-0.05441519791820207</v>
+        <v>0.01802007627663649</v>
       </c>
       <c r="U15">
-        <v>-0.2433137245397242</v>
+        <v>0.2820732968571464</v>
       </c>
       <c r="V15" t="s">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>0.633198997035606</v>
+        <v>1.603126377165344</v>
       </c>
       <c r="X15">
-        <v>0.3354700745776797</v>
+        <v>0.09678024970087273</v>
       </c>
       <c r="Y15">
-        <v>0.2977289224579263</v>
+        <v>0.3000933731337829</v>
       </c>
       <c r="Z15">
-        <v>0.3336536267606375</v>
+        <v>0.05541645779748992</v>
       </c>
       <c r="AA15">
-        <v>0.296116829182692</v>
+        <v>0.1718337346615124</v>
       </c>
       <c r="AB15">
-        <v>1.117160124789949</v>
+        <v>0.7593117840358968</v>
       </c>
       <c r="AC15">
-        <v>72.57746240041317</v>
+        <v>90.83163983910151</v>
       </c>
       <c r="AD15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:30">
@@ -1837,79 +1837,79 @@
         <v>45</v>
       </c>
       <c r="C16">
-        <v>1.276</v>
+        <v>0.552</v>
       </c>
       <c r="D16">
-        <v>1.788</v>
+        <v>0.392</v>
       </c>
       <c r="E16">
-        <v>0.7074963699328916</v>
+        <v>0.2703407362038964</v>
       </c>
       <c r="F16">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="G16">
-        <v>1.523112891688526</v>
+        <v>0.4767959881424244</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
       </c>
       <c r="K16">
-        <v>0.7074963699328916</v>
+        <v>0.2703407362038964</v>
       </c>
       <c r="L16">
-        <v>1.746417103282563</v>
+        <v>0.3921195507989373</v>
       </c>
       <c r="M16">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N16">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="s">
         <v>47</v>
       </c>
       <c r="P16">
-        <v>0.7288501421143858</v>
+        <v>0.3085361649247209</v>
       </c>
       <c r="Q16">
-        <v>1.030182165010288</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="s">
         <v>48</v>
       </c>
       <c r="T16">
-        <v>0.02135377218149426</v>
+        <v>0.03819542872082443</v>
       </c>
       <c r="U16">
-        <v>0.2711498578856142</v>
+        <v>-0.3085361649247209</v>
       </c>
       <c r="V16" t="s">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>1.523112891688526</v>
+        <v>0.4767959881424244</v>
       </c>
       <c r="X16">
-        <v>0.8156165217556348</v>
+        <v>0.206455251938528</v>
       </c>
       <c r="Y16">
-        <v>0.2925036300671084</v>
+        <v>0.2703407362038964</v>
       </c>
       <c r="Z16">
-        <v>0.4670227520233302</v>
+        <v>0.526510987574781</v>
       </c>
       <c r="AA16">
-        <v>0.167487840972995</v>
+        <v>0.6894344738819614</v>
       </c>
       <c r="AB16">
-        <v>0.7593117840358968</v>
+        <v>0.6535325846648956</v>
       </c>
       <c r="AC16">
-        <v>69.61531963599649</v>
+        <v>55.79230620253968</v>
       </c>
       <c r="AD16" t="s">
         <v>49</v>
